--- a/daily/2026-04-03.xlsx
+++ b/daily/2026-04-03.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F59E0B"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -65,6 +80,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1612,7 +1630,6 @@
       <c r="V14" t="n">
         <v>21</v>
       </c>
-      <c r="W14" t="inlineStr"/>
       <c r="X14" t="n">
         <v>6.5</v>
       </c>
@@ -1690,7 +1707,6 @@
       <c r="V15" t="n">
         <v>16</v>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="n">
         <v>-22.4</v>
       </c>
@@ -1842,7 +1858,7 @@
         <v>-1.4</v>
       </c>
       <c r="T17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>15</v>
@@ -1850,7 +1866,6 @@
       <c r="V17" t="n">
         <v>23</v>
       </c>
-      <c r="W17" t="inlineStr"/>
       <c r="X17" t="n">
         <v>-0.6</v>
       </c>
@@ -1928,7 +1943,6 @@
       <c r="V18" t="n">
         <v>16</v>
       </c>
-      <c r="W18" t="inlineStr"/>
       <c r="X18" t="n">
         <v>7.4</v>
       </c>
@@ -2006,7 +2020,6 @@
       <c r="V19" t="n">
         <v>16</v>
       </c>
-      <c r="W19" t="inlineStr"/>
       <c r="X19" t="n">
         <v>0</v>
       </c>
@@ -2084,7 +2097,6 @@
       <c r="V20" t="n">
         <v>16</v>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
         <v>-18.7</v>
       </c>
@@ -2162,7 +2174,6 @@
       <c r="V21" t="n">
         <v>16</v>
       </c>
-      <c r="W21" t="inlineStr"/>
       <c r="X21" t="n">
         <v>2.5</v>
       </c>
@@ -2240,7 +2251,6 @@
       <c r="V22" t="n">
         <v>23</v>
       </c>
-      <c r="W22" t="inlineStr"/>
       <c r="X22" t="n">
         <v>22.7</v>
       </c>
@@ -2638,7 +2648,7 @@
         <v>7.3</v>
       </c>
       <c r="T27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>14</v>
@@ -2646,7 +2656,6 @@
       <c r="V27" t="n">
         <v>16</v>
       </c>
-      <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
         <v>8.5</v>
       </c>
@@ -2888,7 +2897,6 @@
       <c r="V30" t="n">
         <v>7</v>
       </c>
-      <c r="W30" t="inlineStr"/>
       <c r="X30" t="n">
         <v>-9.300000000000001</v>
       </c>
@@ -3212,7 +3220,6 @@
       <c r="V34" t="n">
         <v>30</v>
       </c>
-      <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
         <v>-35.5</v>
       </c>
@@ -3290,7 +3297,6 @@
       <c r="V35" t="n">
         <v>7</v>
       </c>
-      <c r="W35" t="inlineStr"/>
       <c r="X35" t="n">
         <v>-10.8</v>
       </c>
@@ -3368,7 +3374,6 @@
       <c r="V36" t="n">
         <v>7</v>
       </c>
-      <c r="W36" t="inlineStr"/>
       <c r="X36" t="n">
         <v>4.6</v>
       </c>
@@ -3692,7 +3697,6 @@
       <c r="V40" t="n">
         <v>1</v>
       </c>
-      <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
         <v>-32.2</v>
       </c>
@@ -4590,7 +4594,6 @@
       <c r="V51" t="n">
         <v>24</v>
       </c>
-      <c r="W51" t="inlineStr"/>
       <c r="X51" t="n">
         <v>19.6</v>
       </c>
@@ -5799,7 +5802,7 @@
         <v>33</v>
       </c>
       <c r="Q66" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>4.1</v>
@@ -6226,7 +6229,6 @@
       <c r="V71" t="n">
         <v>5</v>
       </c>
-      <c r="W71" t="inlineStr"/>
       <c r="X71" t="n">
         <v>17.3</v>
       </c>
@@ -6304,7 +6306,6 @@
       <c r="V72" t="n">
         <v>25</v>
       </c>
-      <c r="W72" t="inlineStr"/>
       <c r="X72" t="n">
         <v>21.9</v>
       </c>
@@ -6382,7 +6383,6 @@
       <c r="V73" t="n">
         <v>25</v>
       </c>
-      <c r="W73" t="inlineStr"/>
       <c r="X73" t="n">
         <v>0</v>
       </c>
@@ -6460,7 +6460,6 @@
       <c r="V74" t="n">
         <v>5</v>
       </c>
-      <c r="W74" t="inlineStr"/>
       <c r="X74" t="n">
         <v>-4.6</v>
       </c>
@@ -6538,7 +6537,6 @@
       <c r="V75" t="n">
         <v>5</v>
       </c>
-      <c r="W75" t="inlineStr"/>
       <c r="X75" t="n">
         <v>5.8</v>
       </c>
@@ -6616,7 +6614,6 @@
       <c r="V76" t="n">
         <v>5</v>
       </c>
-      <c r="W76" t="inlineStr"/>
       <c r="X76" t="n">
         <v>25.5</v>
       </c>
@@ -6776,7 +6773,6 @@
       <c r="V78" t="n">
         <v>25</v>
       </c>
-      <c r="W78" t="inlineStr"/>
       <c r="X78" t="n">
         <v>2.7</v>
       </c>
@@ -6936,7 +6932,6 @@
       <c r="V80" t="n">
         <v>5</v>
       </c>
-      <c r="W80" t="inlineStr"/>
       <c r="X80" t="n">
         <v>0</v>
       </c>
@@ -7014,7 +7009,6 @@
       <c r="V81" t="n">
         <v>29</v>
       </c>
-      <c r="W81" t="inlineStr"/>
       <c r="X81" t="n">
         <v>-1.7</v>
       </c>
@@ -7174,7 +7168,6 @@
       <c r="V83" t="n">
         <v>29</v>
       </c>
-      <c r="W83" t="inlineStr"/>
       <c r="X83" t="n">
         <v>2</v>
       </c>
@@ -7416,7 +7409,6 @@
       <c r="V86" t="n">
         <v>2</v>
       </c>
-      <c r="W86" t="inlineStr"/>
       <c r="X86" t="n">
         <v>-13.1</v>
       </c>
@@ -7576,7 +7568,6 @@
       <c r="V88" t="n">
         <v>2</v>
       </c>
-      <c r="W88" t="inlineStr"/>
       <c r="X88" t="n">
         <v>-7.8</v>
       </c>
@@ -7736,7 +7727,6 @@
       <c r="V90" t="n">
         <v>29</v>
       </c>
-      <c r="W90" t="inlineStr"/>
       <c r="X90" t="n">
         <v>-14.8</v>
       </c>
@@ -7978,7 +7968,6 @@
       <c r="V93" t="n">
         <v>2</v>
       </c>
-      <c r="W93" t="inlineStr"/>
       <c r="X93" t="n">
         <v>2.2</v>
       </c>
@@ -8056,7 +8045,6 @@
       <c r="V94" t="n">
         <v>15</v>
       </c>
-      <c r="W94" t="inlineStr"/>
       <c r="X94" t="n">
         <v>6.2</v>
       </c>
@@ -8216,7 +8204,6 @@
       <c r="V96" t="n">
         <v>6</v>
       </c>
-      <c r="W96" t="inlineStr"/>
       <c r="X96" t="n">
         <v>-11.2</v>
       </c>
@@ -8376,7 +8363,6 @@
       <c r="V98" t="n">
         <v>15</v>
       </c>
-      <c r="W98" t="inlineStr"/>
       <c r="X98" t="n">
         <v>-0.2</v>
       </c>
@@ -8446,7 +8432,7 @@
         <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U99" t="n">
         <v>25</v>
@@ -8454,7 +8440,6 @@
       <c r="V99" t="n">
         <v>15</v>
       </c>
-      <c r="W99" t="inlineStr"/>
       <c r="X99" t="n">
         <v>8.699999999999999</v>
       </c>
@@ -8532,7 +8517,6 @@
       <c r="V100" t="n">
         <v>6</v>
       </c>
-      <c r="W100" t="inlineStr"/>
       <c r="X100" t="n">
         <v>4.5</v>
       </c>
@@ -8856,7 +8840,6 @@
       <c r="V104" t="n">
         <v>6</v>
       </c>
-      <c r="W104" t="inlineStr"/>
       <c r="X104" t="n">
         <v>3</v>
       </c>
@@ -9016,7 +8999,6 @@
       <c r="V106" t="n">
         <v>6</v>
       </c>
-      <c r="W106" t="inlineStr"/>
       <c r="X106" t="n">
         <v>1.7</v>
       </c>
@@ -14207,2103 +14189,4773 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Quenton Jackson</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Jackson scored 16 pts vs 10.5 line (+5.5), UNDER missed by 5.5 pts. Jackson played 25 min (+9.1 vs L10 avg of 16.1) — 57% more than expected. Shooting efficiency was hot: 75.0% FG (+32.3% vs L10 avg of 42.7%). 6/8 from the field. All 10 agreeing signals (Volume, HR L30, HR L10, Trend) were wrong — result went directly against the consensus. Projection model targeted 8.1 pts — actual 16 was 7.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Pascal Siakam</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E3" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Siakam scored 30 pts vs 21.5 line (+8.5), OVER hit by 8.5 pts. Siakam played 34 min (+4.1 vs L10 avg of 29.8) — 14% more than expected. Shooting was in line with averages: 54.2% FG (13/24, L10 avg 49.4%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 23.2 pts — actual 30 was 6.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Siakam's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>LaMelo Ball</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Ball scored 18 pts vs 19.5 line (-1.5), OVER missed by 1.5 pts. Minutes were as expected: 30 played vs L10 avg 27.9. Shooting was in line with averages: 40.0% FG (6/15, L10 avg 43.4%). Counter-signals that proved correct: Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 22.3 pts — actual 18 was 4.3 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Ben Sheppard</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Sheppard scored 7 pts vs 7.5 line (-0.5), OVER missed by 0.5 pts. Sheppard played 25 min (+5.6 vs L10 avg of 19.0) — 29% more than expected. Shooting efficiency was cold: 28.6% FG (-29.9% vs L10 avg of 58.5%). 2/7 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 8.7 pts — actual 7 was 1.7 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Kon Knueppel</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Knueppel scored 20 pts vs 17.5 line (+2.5), OVER hit by 2.5 pts. Minutes were as expected: 30 played vs L10 avg 28.5. Shooting efficiency was hot: 58.3% FG (+15.5% vs L10 avg of 42.8%). 7/12 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 22.2 pts — actual 20 was 2.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Knueppel's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Obi Toppin</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E7" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Toppin scored 11 pts vs 9.5 line (+1.5), UNDER missed by 1.5 pts. Toppin played 20 min (+3.1 vs L10 avg of 16.9) — 18% more than expected. Shooting efficiency was cold: 44.4% FG (-13.4% vs L10 avg of 57.8%). 4/9 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Defense, H2H, Pace. Projection model targeted 5.4 pts — actual 11 was 5.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Brandon Miller</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E8" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Miller scored 22 pts vs 20.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 30 played vs L10 avg 30.3. Shooting efficiency was hot: 52.9% FG (+7.0% vs L10 avg of 45.9%). 9/17 from the field. Signals that called it correctly: HR L30, Trend, Context, Defense, H2H (7/10 aligned). Counter-signals that were wrong: Volume, HR L10, Min Trend. Projection model targeted 20.7 pts — actual 22 was 1.3 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Miller in this role.</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Miles Bridges</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E9" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Bridges scored 19 pts vs 14.5 line (+4.5), UNDER missed by 4.5 pts. Minutes were as expected: 26 played vs L10 avg 28.0. Shooting efficiency was cold: 43.8% FG (-10.5% vs L10 avg of 54.3%). 7/16 from the field. Counter-signals that proved correct: Volume, Trend, Defense, H2H. Signals that were wrong: HR L30, HR L10, Context. Projection model targeted 13.7 pts — actual 19 was 5.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Kobe Brown</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E10" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Brown scored 12 pts vs 10.5 line (+1.5), UNDER missed by 1.5 pts. Brown played 28 min (+4.6 vs L10 avg of 23.4) — 20% more than expected. Shooting efficiency was cold: 50.0% FG (-5.3% vs L10 avg of 55.3%). 5/10 from the field. Counter-signals that proved correct: Trend, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 5.3 pts — actual 12 was 6.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Moussa Diabaté</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="5" t="n">
         <v>8.5</v>
       </c>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Jay Huff</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E12" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Huff scored 12 pts vs 9.5 line (+2.5), OVER hit by 2.5 pts. Huff played 24 min (+3.0 vs L10 avg of 21.0) — 14% more than expected. Shooting efficiency was cold: 27.8% FG (-24.5% vs L10 avg of 52.3%). 5/18 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 13.3 pts — actual 12 was 1.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Huff in this role.</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Coby White</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — White scored 11 pts vs 15.5 line (-4.5), OVER missed by 4.5 pts. White played 14 min (-6.7 vs L10 avg of 20.9) — 32% less than expected. Shooting efficiency was cold: 42.9% FG (-6.1% vs L10 avg of 49.0%). 3/7 from the field. Counter-signals that proved correct: Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 18.2 pts — actual 11 was 7.2 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag White for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Kam Jones</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jones scored 7 pts vs 7.5 line (-0.5), UNDER hit by 0.5 pts. Jones played 23 min (+3.7 vs L10 avg of 19.1) — 19% more than expected. Shooting efficiency was hot: 60.0% FG (+26.7% vs L10 avg of 33.3%). 3/5 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: H2H, Min Trend. Projection model targeted 2.6 pts — actual 7 was 4.4 pts off (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Paul George</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E15" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — George scored 23 pts vs 16.5 line (+6.5), UNDER missed by 6.5 pts. George played 38 min (+5.4 vs L10 avg of 32.6) — 17% more than expected. Shooting efficiency was cold: 40.0% FG (-7.8% vs L10 avg of 47.8%). 6/15 from the field. Counter-signals that proved correct: Volume, HR L10, Trend, Context. Signals that were wrong: HR L30, Defense, Pace. Projection model targeted 8.0 pts — actual 23 was 15.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Donte DiVincenzo</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E16" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>WIN — DiVincenzo scored 11 pts vs 11.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 29 played vs L10 avg 30.7. Shooting efficiency was cold: 27.3% FG (-8.4% vs L10 avg of 35.7%). 3/11 from the field. Signals that called it correctly: Volume, HR L30, Context, Pace, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 10.9 pts — actual 11 was 0.1 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for DiVincenzo in this role.</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Naz Reid</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E17" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Reid scored 12 pts vs 12.5 line (-0.5), OVER missed by 0.5 pts. Minutes were as expected: 29 played vs L10 avg 26.1. Shooting efficiency was cold: 35.7% FG (-5.1% vs L10 avg of 40.8%). 5/14 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Defense. Signals that were wrong: Trend, Context. Projection model targeted 15.6 pts — actual 12 was 3.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Tyrese Maxey</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>26.5</v>
       </c>
+      <c r="E18" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Maxey scored 21 pts vs 26.5 line (-5.5), OVER missed by 5.5 pts. Minutes were as expected: 35 played vs L10 avg 37.2. Shooting efficiency was hot: 53.8% FG (+8.2% vs L10 avg of 45.6%). 7/13 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 35.8 pts — actual 21 was 14.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Joel Embiid</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>28.5</v>
       </c>
+      <c r="E19" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Embiid scored 19 pts vs 28.5 line (-9.5), OVER missed by 9.5 pts. Minutes were as expected: 34 played vs L10 avg 33.4. Shooting efficiency was cold: 35.3% FG (-17.2% vs L10 avg of 52.5%). 6/17 from the field. Counter-signals that proved correct: Volume, HR L30, Defense, H2H. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 29.8 pts — actual 19 was 10.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Dominick Barlow</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="E20" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Barlow scored 7 pts vs 5.5 line (+1.5), UNDER missed by 1.5 pts. Barlow played 26 min (+3.7 vs L10 avg of 22.1) — 17% more than expected. Shooting was in line with averages: 60.0% FG (3/5, L10 avg 59.9%). Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Pace. Projection model targeted 3.5 pts — actual 7 was 3.5 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Kelly Oubre Jr.</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E21" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 21 pts vs 9.5 line (+11.5), OVER hit by 11.5 pts. Minutes were as expected: 30 played vs L10 avg 29.8. Shooting efficiency was hot: 66.7% FG (+21.4% vs L10 avg of 45.3%). 8/12 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, FG Trend (5/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 17.7 pts — actual 21 was 3.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jr.'s consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Rudy Gobert</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E22" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Gobert scored 5 pts vs 11.5 line (-6.5), OVER missed by 6.5 pts. Minutes were as expected: 29 played vs L10 avg 31.1. Shooting efficiency was cold: 25.0% FG (-37.9% vs L10 avg of 62.9%). 2/8 from the field. Counter-signals that proved correct: Volume, HR L30, Defense, H2H. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 20.6 pts — actual 5 was 15.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Ayo Dosunmu</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E23" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Dosunmu scored 19 pts vs 15.5 line (+3.5), UNDER missed by 3.5 pts. Dosunmu played 36 min (+6.0 vs L10 avg of 30.2) — 20% more than expected. Shooting efficiency was cold: 37.5% FG (-15.9% vs L10 avg of 53.4%). 6/16 from the field. Counter-signals that proved correct: HR L30, HR L10, Trend, Defense. Signals that were wrong: Volume, Context, H2H. Projection model targeted 11.7 pts — actual 19 was 7.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Quentin Grimes</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E24" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Grimes scored 10 pts vs 8.5 line (+1.5), OVER hit by 1.5 pts. Grimes played 25 min (-6.6 vs L10 avg of 31.4) — 21% less than expected. Shooting efficiency was hot: 62.5% FG (+15.2% vs L10 avg of 47.3%). 5/8 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, FG Trend. Projection model targeted 18.4 pts — actual 10 was 8.4 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Grimes's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Anthony Edwards</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>24.5</v>
       </c>
+      <c r="E25" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Edwards scored 8 pts vs 24.5 line (-16.5), OVER missed by 16.5 pts. Edwards played 26 min (-7.9 vs L10 avg of 34.1) — 23% less than expected. Shooting efficiency was cold: 20.0% FG (-28.6% vs L10 avg of 48.6%). 3/15 from the field. Counter-signals that proved correct: HR L10, Trend, Pace, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 25.0 pts — actual 8 was 17.0 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Edwards for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Julius Randle</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E26" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Randle scored 21 pts vs 20.5 line (+0.5), UNDER missed by 0.5 pts. Randle played 37 min (+4.1 vs L10 avg of 32.7) — 13% more than expected. Shooting efficiency was hot: 60.0% FG (+12.5% vs L10 avg of 47.5%). 9/15 from the field. Counter-signals that proved correct: HR L10, Defense, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, Trend. Projection model targeted 13.8 pts — actual 21 was 7.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>VJ Edgecombe</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E27" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Edgecombe scored 8 pts vs 13.5 line (-5.5), OVER missed by 5.5 pts. Edgecombe played 37 min (+3.5 vs L10 avg of 33.3) — 11% more than expected. Shooting efficiency was cold: 44.4% FG (-7.8% vs L10 avg of 52.2%). 4/9 from the field. Counter-signals that proved correct: Defense, H2H, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 22.9 pts — actual 8 was 14.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Onyeka Okongwu</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E28" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Okongwu scored 15 pts vs 14.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 27 played vs L10 avg 29.2. Shooting was in line with averages: 45.5% FG (5/11, L10 avg 45.3%). Counter-signals that proved correct: Volume, HR L30, Defense, H2H. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 14.2 pts — actual 15 was 0.8 pts close (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>CJ McCollum</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E29" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — McCollum scored 25 pts vs 17.5 line (+7.5), UNDER missed by 7.5 pts. McCollum played 25 min (-4.5 vs L10 avg of 29.9) — 15% less than expected. Shooting efficiency was hot: 66.7% FG (+20.3% vs L10 avg of 46.4%). 8/12 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, H2H, Pace. Projection model targeted 14.7 pts — actual 25 was 10.3 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag McCollum for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Nolan Traore</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E30" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Traore scored 13 pts vs 11.5 line (+1.5), OVER hit by 1.5 pts. Traore played 30 min (+7.5 vs L10 avg of 22.0) — 34% more than expected. Shooting efficiency was hot: 45.5% FG (+17.5% vs L10 avg of 28.0%). 5/11 from the field. Signals that called it correctly: Context, Defense, Pace (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 12.5 pts — actual 13 was 0.5 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Traore in this role.</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E31" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Alexander-Walker scored 21 pts vs 19.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 34 played vs L10 avg 33.0. Shooting was in line with averages: 50.0% FG (8/16, L10 avg 53.4%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: H2H, Pace, Min Trend. Projection model targeted 21.0 pts — actual 21 was 0.0 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Alexander-Walker in this role.</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Noah Clowney</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E32" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Clowney scored 12 pts vs 10.5 line (+1.5), UNDER missed by 1.5 pts. Minutes were as expected: 21 played vs L10 avg 21.4. Shooting efficiency was hot: 57.1% FG (+23.6% vs L10 avg of 33.5%). 4/7 from the field. Counter-signals that proved correct: Volume, Defense, Pace. Signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 8.3 pts — actual 12 was 3.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Jalen Johnson</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E33" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Johnson scored 18 pts vs 22.5 line (-4.5), UNDER hit by 4.5 pts. Johnson played 28 min (-8.7 vs L10 avg of 36.2) — 24% less than expected. Shooting was in line with averages: 50.0% FG (6/12, L10 avg 48.2%). Signals that called it correctly: Volume, Context, H2H, Pace (4/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 19.9 pts — actual 18 was 1.9 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Johnson in this role.</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Jonathan Kuminga</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E34" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Kuminga scored 12 pts vs 12.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 20 played vs L10 avg 20.3. Shooting efficiency was hot: 66.7% FG (+28.1% vs L10 avg of 38.6%). 4/6 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: Defense, H2H. Projection model targeted 2.4 pts — actual 12 was 9.6 pts off (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Drake Powell</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E35" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Powell scored 6 pts vs 8.5 line (-2.5), OVER missed by 2.5 pts. Powell played 29 min (+3.1 vs L10 avg of 25.5) — 12% more than expected. Shooting efficiency was cold: 28.6% FG (-11.9% vs L10 avg of 40.5%). 2/7 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Pace. Projection model targeted 8.8 pts — actual 6 was 2.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Ziaire Williams</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E36" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Williams scored 8 pts vs 10.5 line (-2.5), OVER missed by 2.5 pts. Minutes were as expected: 21 played vs L10 avg 22.4. Shooting efficiency was cold: 20.0% FG (-27.9% vs L10 avg of 47.9%). 2/10 from the field. Counter-signals that proved correct: H2H, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.6 pts — actual 8 was 3.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Dyson Daniels</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E37" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Daniels scored 11 pts vs 11.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 30 played vs L10 avg 32.2. Shooting efficiency was hot: 62.5% FG (+7.3% vs L10 avg of 55.2%). 5/8 from the field. Signals that called it correctly: Context, H2H, Pace (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.5 pts — actual 11 was 1.5 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Daniels in this role.</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Zaccharie Risacher</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Risacher scored 2 pts vs 7.5 line (-5.5), OVER missed by 5.5 pts. Risacher played 12 min (-4.0 vs L10 avg of 16.5) — 24% less than expected. Shooting efficiency was cold: 33.3% FG (-29.1% vs L10 avg of 62.4%). 1/3 from the field. Counter-signals that proved correct: HR L30, HR L10, Trend, Pace. Signals that were wrong: Volume, Context, Defense. Projection model targeted 10.8 pts — actual 2 was 8.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Matas Buzelis</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E39" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Buzelis scored 11 pts vs 17.5 line (-6.5), UNDER hit by 6.5 pts. Buzelis played 23 min (-9.3 vs L10 avg of 32.5) — 29% less than expected. Shooting was in line with averages: 44.4% FG (4/9, L10 avg 43.7%). Signals that called it correctly: Trend, Defense, H2H, Pace, FG Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 14.8 pts — actual 11 was 3.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Buzelis's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Mitchell Robinson</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E40" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Robinson scored 17 pts vs 6.5 line (+10.5), UNDER missed by 10.5 pts. Minutes were as expected: 23 played vs L10 avg 21.1. Shooting efficiency was hot: 100.0% FG (+25.2% vs L10 avg of 74.8%). 7/7 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 2.4 pts — actual 17 was 14.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Isaac Okoro</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E41" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Okoro scored 7 pts vs 8.5 line (-1.5), OVER missed by 1.5 pts. Okoro played 26 min (-3.3 vs L10 avg of 29.7) — 11% less than expected. Shooting was in line with averages: 50.0% FG (3/6, L10 avg 45.1%). Counter-signals that proved correct: HR L10, Defense, Pace. Signals that were wrong: Volume, HR L30, Trend. Projection model targeted 11.3 pts — actual 7 was 4.3 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Josh Hart</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E42" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Hart scored 7 pts vs 12.5 line (-5.5), UNDER hit by 5.5 pts. Minutes were as expected: 28 played vs L10 avg 30.9. Shooting was in line with averages: 60.0% FG (3/5, L10 avg 56.8%). Signals that called it correctly: Volume, HR L30, Trend, Context, H2H (5/10 aligned). Counter-signals that were wrong: HR L10, Defense, Pace. Projection model targeted 6.1 pts — actual 7 was 0.9 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Hart in this role.</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Tre Jones</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E43" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jones scored 13 pts vs 13.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 26 played vs L10 avg 27.6. Shooting efficiency was hot: 80.0% FG (+21.1% vs L10 avg of 58.9%). 4/5 from the field. Signals that called it correctly: Defense, H2H, Pace (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 13.0 pts — actual 13 was 0.0 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Jones in this role.</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>OG Anunoby</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E44" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Anunoby scored 31 pts vs 17.5 line (+13.5), UNDER missed by 13.5 pts. Anunoby played 30 min (-4.1 vs L10 avg of 34.6) — 12% less than expected. Shooting efficiency was hot: 60.0% FG (+12.0% vs L10 avg of 48.0%). 9/15 from the field. Counter-signals that proved correct: Volume, HR L30, Defense, Pace. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 16.5 pts — actual 31 was 14.5 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Anunoby for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Karl-Anthony Towns</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="5" t="n">
         <v>20.5</v>
       </c>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="inlineStr"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Mikal Bridges</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E46" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Bridges scored 12 pts vs 14.5 line (-2.5), UNDER hit by 2.5 pts. Bridges played 23 min (-9.6 vs L10 avg of 32.3) — 30% less than expected. Shooting efficiency was cold: 33.3% FG (-15.3% vs L10 avg of 48.6%). 4/12 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context (4/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 12.1 pts — actual 12 was 0.1 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Bridges in this role.</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Nick Richards</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="5" t="n">
         <v>8.5</v>
       </c>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="inlineStr"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Josh Giddey</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E48" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Giddey scored 6 pts vs 15.5 line (-9.5), OVER missed by 9.5 pts. Giddey played 26 min (-9.3 vs L10 avg of 35.0) — 27% less than expected. Shooting efficiency was cold: 25.0% FG (-18.0% vs L10 avg of 43.0%). 3/12 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, H2H, FG Trend. Projection model targeted 17.0 pts — actual 6 was 11.0 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Giddey for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Jalen Brunson</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="4" t="n">
         <v>26.5</v>
       </c>
+      <c r="E49" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Brunson scored 17 pts vs 26.5 line (-9.5), UNDER hit by 9.5 pts. Brunson played 30 min (-6.7 vs L10 avg of 36.6) — 18% less than expected. Shooting was in line with averages: 46.2% FG (6/13, L10 avg 46.5%). Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 24.7 pts — actual 17 was 7.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Brunson's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>Ryan Rollins</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="5" t="n">
         <v>18.5</v>
       </c>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="inlineStr"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Ousmane Dieng</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E51" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Dieng scored 9 pts vs 12.5 line (-3.5), UNDER hit by 3.5 pts. Dieng played 24 min (-5.3 vs L10 avg of 29.3) — 18% less than expected. Shooting efficiency was cold: 26.7% FG (-14.8% vs L10 avg of 41.5%). 4/15 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (6/10 aligned). Counter-signals that were wrong: Trend, H2H, FG Trend. Projection model targeted 12.4 pts — actual 9 was 3.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Dieng's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Sam Hauser</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E52" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Hauser scored 13 pts vs 8.5 line (+4.5), UNDER missed by 4.5 pts. Minutes were as expected: 27 played vs L10 avg 25.1. Shooting efficiency was hot: 83.3% FG (+44.3% vs L10 avg of 39.0%). 5/6 from the field. Counter-signals that proved correct: Volume, HR L30, Trend, Defense. Signals that were wrong: HR L10, Context, H2H. Projection model targeted 6.7 pts — actual 13 was 6.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Payton Pritchard</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E53" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Pritchard scored 16 pts vs 16.5 line (-0.5), OVER missed by 0.5 pts. Pritchard played 26 min (-5.3 vs L10 avg of 31.8) — 17% less than expected. Shooting efficiency was hot: 58.3% FG (+13.8% vs L10 avg of 44.5%). 7/12 from the field. Counter-signals that proved correct: HR L10, H2H, Min Trend. Signals that were wrong: Volume, HR L30, Trend. Projection model targeted 17.0 pts — actual 16 was 1.0 pts close (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Pritchard for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>Gary Trent Jr.</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="5" t="n">
         <v>10.5</v>
       </c>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="inlineStr"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Myles Turner</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E55" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Turner scored 4 pts vs 10.5 line (-6.5), UNDER hit by 6.5 pts. Turner played 19 min (-5.7 vs L10 avg of 24.5) — 23% less than expected. Shooting efficiency was cold: 25.0% FG (-15.7% vs L10 avg of 40.7%). 1/4 from the field. Signals that called it correctly: HR L30, HR L10, Trend, Context, Defense (9/10 aligned). Counter-signals that were wrong: Volume. Projection model targeted 5.2 pts — actual 4 was 1.2 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Jaylen Brown</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="4" t="n">
         <v>25.5</v>
       </c>
+      <c r="E56" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Brown scored 26 pts vs 25.5 line (+0.5), OVER hit by 0.5 pts. Brown played 30 min (-4.8 vs L10 avg of 35.0) — 14% less than expected. Shooting efficiency was cold: 41.2% FG (-5.0% vs L10 avg of 46.2%). 7/17 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (9/10 aligned). Counter-signals that were wrong: FG Trend. Projection model targeted 27.2 pts — actual 26 was 1.2 pts close (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Neemias Queta</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E57" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Queta scored 19 pts vs 9.5 line (+9.5), UNDER missed by 9.5 pts. Minutes were as expected: 29 played vs L10 avg 28.3. Shooting efficiency was hot: 72.7% FG (+6.6% vs L10 avg of 66.1%). 8/11 from the field. Counter-signals that proved correct: Volume, HR L10, Trend, Pace. Signals that were wrong: HR L30, Context, Defense. Projection model targeted 7.6 pts — actual 19 was 11.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Kyle Kuzma</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E58" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Kuzma scored 14 pts vs 12.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 25 played vs L10 avg 25.2. Shooting efficiency was cold: 42.9% FG (-8.2% vs L10 avg of 51.1%). 6/14 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 18.1 pts — actual 14 was 4.1 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Kuzma's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Jayson Tatum</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E59" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Tatum scored 23 pts vs 22.5 line (+0.5), OVER hit by 0.5 pts. Minutes were as expected: 31 played vs L10 avg 32.4. Shooting efficiency was hot: 50.0% FG (+9.8% vs L10 avg of 40.2%). 8/16 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 22.6 pts — actual 23 was 0.4 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Tatum in this role.</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>Derrick White</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E60" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — White scored 17 pts vs 15.5 line (+1.5), UNDER missed by 1.5 pts. Minutes were as expected: 32 played vs L10 avg 34.4. Shooting efficiency was hot: 54.5% FG (+13.7% vs L10 avg of 40.8%). 6/11 from the field. Counter-signals that proved correct: Volume, Defense, Pace, FG Trend. Signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 11.7 pts — actual 17 was 5.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>Amen Thompson</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="3" t="n">
         <v>18.5</v>
       </c>
+      <c r="E61" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Thompson scored 21 pts vs 18.5 line (+2.5), UNDER missed by 2.5 pts. Thompson played 32 min (-7.3 vs L10 avg of 39.2) — 19% less than expected. Shooting efficiency was hot: 63.6% FG (+8.7% vs L10 avg of 54.9%). 7/11 from the field. Counter-signals that proved correct: Defense, Pace, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 17.4 pts — actual 21 was 3.6 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Thompson for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Kyle Filipowski</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E62" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Filipowski scored 17 pts vs 15.5 line (+1.5), UNDER missed by 1.5 pts. Filipowski played 30 min (+4.5 vs L10 avg of 25.8) — 17% more than expected. Shooting was in line with averages: 50.0% FG (8/16, L10 avg 50.2%). Counter-signals that proved correct: HR L10, Trend, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 13.0 pts — actual 17 was 4.0 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Cody Williams</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E63" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Williams scored 27 pts vs 14.5 line (+12.5), UNDER missed by 12.5 pts. Williams played 38 min (+5.1 vs L10 avg of 33.2) — 15% more than expected. Shooting efficiency was hot: 62.5% FG (+17.9% vs L10 avg of 44.6%). 10/16 from the field. Counter-signals that proved correct: HR L10, Trend, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 11.5 pts — actual 27 was 15.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>Ace Bailey</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="3" t="n">
         <v>18.5</v>
       </c>
+      <c r="E64" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Bailey scored 22 pts vs 18.5 line (+3.5), UNDER missed by 3.5 pts. Bailey played 33 min (+3.3 vs L10 avg of 29.3) — 11% more than expected. Shooting was in line with averages: 52.9% FG (9/17, L10 avg 48.5%). Counter-signals that proved correct: FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 15.4 pts — actual 22 was 6.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Jabari Smith Jr.</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E65" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 18 pts vs 15.5 line (+2.5), OVER hit by 2.5 pts. Jr. played 24 min (-13.7 vs L10 avg of 37.7) — 36% less than expected. Shooting was in line with averages: 37.5% FG (6/16, L10 avg 42.1%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: H2H, FG Trend. Projection model targeted 16.3 pts — actual 18 was 1.7 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>Alperen Sengun</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E66" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Sengun scored 19 pts vs 19.5 line (-0.5), OVER missed by 0.5 pts. Sengun played 28 min (-5.4 vs L10 avg of 33.0) — 16% less than expected. Shooting was in line with averages: 66.7% FG (8/12, L10 avg 64.8%). Counter-signals that proved correct: Volume, HR L30, HR L10. Signals that were wrong: Trend, Context, Defense. Projection model targeted 23.6 pts — actual 19 was 4.6 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Sengun for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>Tari Eason</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E67" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Eason scored 16 pts vs 10.5 line (+5.5), OVER hit by 5.5 pts. Eason played 22 min (-3.2 vs L10 avg of 25.1) — 13% less than expected. Shooting efficiency was hot: 70.0% FG (+38.9% vs L10 avg of 31.1%). 7/10 from the field. Signals that called it correctly: Trend, Defense, H2H, Pace (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.3 pts — actual 16 was 4.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Eason's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>Reed Sheppard</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E68" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Sheppard scored 12 pts vs 15.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 29 played vs L10 avg 29.8. Shooting was in line with averages: 40.0% FG (4/10, L10 avg 44.8%). Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (5/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 15.7 pts — actual 12 was 3.7 pts off (wrong direction). Result classification: MODEL_CORRECT. Note: Result confirms Sheppard's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Kevin Durant</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="3" t="n">
         <v>23.5</v>
       </c>
+      <c r="E69" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Durant scored 25 pts vs 23.5 line (+1.5), UNDER missed by 1.5 pts. Durant played 30 min (-5.8 vs L10 avg of 36.2) — 16% less than expected. Shooting efficiency was hot: 66.7% FG (+13.4% vs L10 avg of 53.3%). 8/12 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend. Projection model targeted 23.0 pts — actual 25 was 2.0 pts close (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Durant for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>Brice Sensabaugh</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E70" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Sensabaugh scored 20 pts vs 20.5 line (-0.5), UNDER hit by 0.5 pts. Sensabaugh played 33 min (+3.7 vs L10 avg of 29.7) — 12% more than expected. Shooting efficiency was cold: 43.8% FG (-9.5% vs L10 avg of 53.3%). 7/16 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 19.4 pts — actual 20 was 0.6 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Sensabaugh in this role.</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>Brandon Ingram</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E71" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Ingram scored 17 pts vs 21.5 line (-4.5), UNDER hit by 4.5 pts. Ingram played 26 min (-8.0 vs L10 avg of 34.1) — 23% less than expected. Shooting efficiency was hot: 54.5% FG (+6.1% vs L10 avg of 48.4%). 6/11 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (5/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 19.4 pts — actual 17 was 2.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Ingram's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>GG Jackson</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E72" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jackson scored 30 pts vs 15.5 line (+14.5), OVER hit by 14.5 pts. Jackson played 30 min (+4.2 vs L10 avg of 25.9) — 16% more than expected. Shooting efficiency was hot: 62.5% FG (+11.1% vs L10 avg of 51.4%). 10/16 from the field. Signals that called it correctly: Volume, HR L10, Context, Min Trend (4/10 aligned). Counter-signals that were wrong: HR L30, Trend, Defense. Projection model targeted 18.6 pts — actual 30 was 11.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jackson's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>Taylor Hendricks</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E73" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Hendricks scored 9 pts vs 9.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 26 played vs L10 avg 25.4. Shooting was in line with averages: 40.0% FG (4/10, L10 avg 41.4%). Signals that called it correctly: Volume, HR L30, Trend, Context, Defense (7/10 aligned). Counter-signals that were wrong: HR L10, H2H, Min Trend. Projection model targeted 8.6 pts — actual 9 was 0.4 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Hendricks in this role.</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>Ja'Kobe Walter</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E74" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Walter scored 7 pts vs 10.5 line (-3.5), UNDER hit by 3.5 pts. Walter played 28 min (+3.2 vs L10 avg of 24.6) — 13% more than expected. Shooting efficiency was cold: 22.2% FG (-35.4% vs L10 avg of 57.6%). 2/9 from the field. Signals that called it correctly: Volume, HR L30, Context (3/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 6.9 pts — actual 7 was 0.1 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Walter in this role.</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>RJ Barrett</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E75" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Barrett scored 25 pts vs 21.5 line (+3.5), OVER hit by 3.5 pts. Minutes were as expected: 29 played vs L10 avg 30.5. Shooting was in line with averages: 52.9% FG (9/17, L10 avg 53.1%). Signals that called it correctly: Trend, Defense, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 25.0 pts — actual 25 was 0.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Barrett in this role.</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>Jamal Shead</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E76" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Shead scored 11 pts vs 7.5 line (+3.5), OVER hit by 3.5 pts. Minutes were as expected: 23 played vs L10 avg 25.9. Shooting efficiency was hot: 66.7% FG (+36.6% vs L10 avg of 30.1%). 2/3 from the field. Signals that called it correctly: Trend, Defense, Pace, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.2 pts — actual 11 was 1.8 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Shead in this role.</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>Scottie Barnes</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E77" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Barnes scored 10 pts vs 18.5 line (-8.5), UNDER hit by 8.5 pts. Barnes played 23 min (-8.0 vs L10 avg of 31.3) — 26% less than expected. Shooting efficiency was hot: 66.7% FG (+12.1% vs L10 avg of 54.6%). 4/6 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 16.7 pts — actual 10 was 6.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Barnes's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>Cedric Coward</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E78" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Coward scored 15 pts vs 14.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 27 played vs L10 avg 24.9. Shooting was in line with averages: 45.5% FG (5/11, L10 avg 43.3%). Counter-signals that proved correct: HR L10, Trend, H2H. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 11.5 pts — actual 15 was 3.5 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>Sandro Mamukelashvili</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E79" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Mamukelashvili scored 10 pts vs 11.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 21 played vs L10 avg 21.4. Shooting efficiency was cold: 40.0% FG (-20.2% vs L10 avg of 60.2%). 2/5 from the field. Signals that called it correctly: HR L30, Context, H2H, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L10, Trend. Projection model targeted 9.7 pts — actual 10 was 0.3 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Mamukelashvili in this role.</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>Jakob Poeltl</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E80" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Poeltl scored 8 pts vs 11.5 line (-3.5), UNDER hit by 3.5 pts. Poeltl played 23 min (-3.0 vs L10 avg of 25.8) — 12% less than expected. Shooting was in line with averages: 66.7% FG (4/6, L10 avg 62.7%). Signals that called it correctly: Volume, HR L30, Context, FG Trend (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 10.8 pts — actual 8 was 2.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Poeltl's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>Brandon Williams</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E81" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Williams scored 23 pts vs 13.5 line (+9.5), UNDER missed by 9.5 pts. Williams played 26 min (+4.8 vs L10 avg of 20.8) — 23% more than expected. Shooting was in line with averages: 46.7% FG (7/15, L10 avg 44.7%). Counter-signals that proved correct: Volume, HR L30, Defense, H2H. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 10.6 pts — actual 23 was 12.4 pts off (correct direction). Loss classification: BLOWOUT_EFFECT. Note: Game script invalidated the prop. Consider blowout probability when DAL is involved.</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>Wendell Carter Jr.</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E82" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 28 pts vs 11.5 line (+16.5), OVER hit by 16.5 pts. Jr. played 36 min (+6.6 vs L10 avg of 29.3) — 23% more than expected. Shooting efficiency was cold: 50.0% FG (-5.0% vs L10 avg of 55.0%). 8/16 from the field. Signals that called it correctly: HR L10, Trend, Context, Defense, Pace (7/10 aligned). Counter-signals that were wrong: Volume, HR L30, H2H. Projection model targeted 11.8 pts — actual 28 was 16.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jr.'s consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>Daniel Gafford</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E83" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Gafford scored 7 pts vs 11.5 line (-4.5), OVER missed by 4.5 pts. Gafford played 20 min (-3.7 vs L10 avg of 23.6) — 16% less than expected. Shooting efficiency was cold: 66.7% FG (-6.3% vs L10 avg of 73.0%). 2/3 from the field. Counter-signals that proved correct: Volume, HR L30, Defense, H2H. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 16.7 pts — actual 7 was 9.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>Desmond Bane</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E84" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Bane scored 27 pts vs 20.5 line (+6.5), OVER hit by 6.5 pts. Minutes were as expected: 33 played vs L10 avg 32.7. Shooting efficiency was hot: 61.5% FG (+16.9% vs L10 avg of 44.6%). 8/13 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, Pace (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 20.9 pts — actual 27 was 6.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Bane's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>Klay Thompson</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E85" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Thompson scored 18 pts vs 9.5 line (+8.5), OVER hit by 8.5 pts. Minutes were as expected: 22 played vs L10 avg 21.1. Shooting efficiency was hot: 53.8% FG (+13.8% vs L10 avg of 40.0%). 7/13 from the field. Signals that called it correctly: Volume, Context, Defense, H2H (4/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 11.4 pts — actual 18 was 6.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Thompson's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>Franz Wagner</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E86" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Wagner scored 18 pts vs 15.5 line (+2.5), UNDER missed by 2.5 pts. Wagner played 17 min (-8.5 vs L10 avg of 25.6) — 33% less than expected. Shooting efficiency was hot: 66.7% FG (+19.3% vs L10 avg of 47.4%). 8/12 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, FG Trend, Min Trend. Projection model targeted 13.6 pts — actual 18 was 4.4 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Wagner for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>Naji Marshall</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E87" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Marshall scored 9 pts vs 16.5 line (-7.5), UNDER hit by 7.5 pts. Marshall played 24 min (-7.1 vs L10 avg of 30.8) — 23% less than expected. Shooting efficiency was cold: 25.0% FG (-21.5% vs L10 avg of 46.5%). 3/12 from the field. Signals that called it correctly: Defense, H2H, Pace, FG Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 7.6 pts — actual 9 was 1.4 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Marshall in this role.</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>Jalen Suggs</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E88" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Suggs scored 19 pts vs 14.5 line (+4.5), UNDER missed by 4.5 pts. Minutes were as expected: 31 played vs L10 avg 30.9. Shooting efficiency was hot: 66.7% FG (+24.3% vs L10 avg of 42.4%). 8/12 from the field. Counter-signals that proved correct: Defense, H2H, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.1 pts — actual 19 was 7.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>Khris Middleton</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Middleton scored 0 pts vs 9.5 line (-9.5), UNDER hit by 9.5 pts. Middleton played 12 min (-7.0 vs L10 avg of 19.2) — 36% less than expected. Shooting efficiency was cold: 0.0% FG (-35.4% vs L10 avg of 35.4%). 0/4 from the field. Signals that called it correctly: HR L10, Trend, Defense, Pace, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 9.4 pts — actual 0 was 9.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Middleton's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>Cooper Flagg</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="3" t="n">
         <v>23.5</v>
       </c>
+      <c r="E90" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Flagg scored 51 pts vs 23.5 line (+27.5), UNDER missed by 27.5 pts. Minutes were as expected: 34 played vs L10 avg 34.4. Shooting efficiency was hot: 63.3% FG (+16.9% vs L10 avg of 46.4%). 19/30 from the field. Counter-signals that proved correct: HR L10, Trend, H2H, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 19.8 pts — actual 51 was 31.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>Max Christie</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E91" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Christie scored 14 pts vs 9.5 line (+4.5), UNDER missed by 4.5 pts. Minutes were as expected: 28 played vs L10 avg 28.6. Shooting efficiency was hot: 57.1% FG (+12.8% vs L10 avg of 44.3%). 4/7 from the field. Counter-signals that proved correct: Volume, HR L30, Context, Defense. Signals that were wrong: HR L10, Trend, H2H. Projection model targeted 7.1 pts — actual 14 was 6.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>Tristan da Silva</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E92" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Silva scored 19 pts vs 8.5 line (+10.5), OVER hit by 10.5 pts. Minutes were as expected: 29 played vs L10 avg 27.8. Shooting efficiency was hot: 54.5% FG (+11.0% vs L10 avg of 43.5%). 6/11 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: FG Trend, Min Trend. Projection model targeted 11.3 pts — actual 19 was 7.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>Paolo Banchero</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="4" t="n">
         <v>23.5</v>
       </c>
+      <c r="E93" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Banchero scored 10 pts vs 23.5 line (-13.5), UNDER hit by 13.5 pts. Banchero played 31 min (-3.0 vs L10 avg of 34.1) — 9% less than expected. Shooting was in line with averages: 40.0% FG (4/10, L10 avg 39.5%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 22.7 pts — actual 10 was 12.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Banchero's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>Jeremiah Fears</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E94" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Fears scored 28 pts vs 14.5 line (+13.5), OVER hit by 13.5 pts. Fears played 37 min (+14.9 vs L10 avg of 22.1) — 67% more than expected. Shooting efficiency was hot: 52.6% FG (+6.0% vs L10 avg of 46.6%). 10/19 from the field. Signals that called it correctly: Trend, Defense, FG Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 15.8 pts — actual 28 was 12.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Fears's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>DeMar DeRozan</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E95" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>WIN — DeRozan scored 14 pts vs 20.5 line (-6.5), UNDER hit by 6.5 pts. DeRozan played 24 min (-8.5 vs L10 avg of 32.0) — 27% less than expected. Shooting efficiency was hot: 63.6% FG (+13.1% vs L10 avg of 50.5%). 7/11 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 16.8 pts — actual 14 was 2.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms DeRozan's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>Nique Clifford</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E96" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Clifford scored 23 pts vs 12.5 line (+10.5), UNDER missed by 10.5 pts. Clifford played 39 min (+5.8 vs L10 avg of 32.8) — 18% more than expected. Shooting efficiency was hot: 56.2% FG (+14.6% vs L10 avg of 41.6%). 9/16 from the field. Counter-signals that proved correct: Defense, H2H, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 12.2 pts — actual 23 was 10.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>Zion Williamson</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="3" t="n">
         <v>21.5</v>
       </c>
+      <c r="E97" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Williamson scored 13 pts vs 21.5 line (-8.5), OVER missed by 8.5 pts. Minutes were as expected: 28 played vs L10 avg 30.6. Shooting efficiency was cold: 45.5% FG (-26.0% vs L10 avg of 71.5%). 5/11 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Defense, H2H, FG Trend. Projection model targeted 25.1 pts — actual 13 was 12.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>Derik Queen</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E98" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Queen scored 8 pts vs 11.5 line (-3.5), UNDER hit by 3.5 pts. Queen played 28 min (+8.0 vs L10 avg of 19.6) — 41% more than expected. Shooting efficiency was cold: 30.0% FG (-9.1% vs L10 avg of 39.1%). 3/10 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, FG Trend (6/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 9.5 pts — actual 8 was 1.5 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Queen in this role.</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>Saddiq Bey</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E99" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Bey scored 20 pts vs 19.5 line (+0.5), UNDER missed by 0.5 pts. Bey played 29 min (-3.5 vs L10 avg of 32.7) — 11% less than expected. Shooting was in line with averages: 46.7% FG (7/15, L10 avg 44.7%). Counter-signals that proved correct: Volume, Defense, H2H, Pace. Signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 17.5 pts — actual 20 was 2.5 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>Devin Carter</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E100" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Carter scored 9 pts vs 13.5 line (-4.5), OVER missed by 4.5 pts. Carter played 32 min (+11.0 vs L10 avg of 20.7) — 53% more than expected. Shooting efficiency was cold: 30.0% FG (-8.6% vs L10 avg of 38.6%). 3/10 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Pace. Projection model targeted 15.5 pts — actual 9 was 6.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>Yves Missi</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E101" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Missi scored 6 pts vs 6.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 20 played vs L10 avg 22.6. Shooting efficiency was cold: 40.0% FG (-8.6% vs L10 avg of 48.6%). 2/5 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, Min Trend. Projection model targeted 3.7 pts — actual 6 was 2.3 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Missi's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>Precious Achiuwa</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E102" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Achiuwa scored 12 pts vs 15.5 line (-3.5), OVER missed by 3.5 pts. Achiuwa played 25 min (-6.9 vs L10 avg of 31.8) — 22% less than expected. Shooting was in line with averages: 60.0% FG (6/10, L10 avg 57.6%). Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Pace. Projection model targeted 19.1 pts — actual 12 was 7.1 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Achiuwa for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>Herbert Jones</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E103" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jones scored 3 pts vs 9.5 line (-6.5), UNDER hit by 6.5 pts. Jones played 13 min (-17.0 vs L10 avg of 29.8) — 57% less than expected. Shooting was in line with averages: 33.3% FG (1/3, L10 avg 37.2%). Signals that called it correctly: Volume, HR L30, Context, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 8.8 pts — actual 3 was 5.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jones's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="4" t="inlineStr">
         <is>
           <t>Maxime Raynaud</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E104" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Raynaud scored 28 pts vs 14.5 line (+13.5), OVER hit by 13.5 pts. Raynaud played 29 min (-3.7 vs L10 avg of 32.7) — 11% less than expected. Shooting efficiency was hot: 78.6% FG (+21.1% vs L10 avg of 57.5%). 11/14 from the field. Signals that called it correctly: Volume, HR L10, Context, Defense, Pace (6/10 aligned). Counter-signals that were wrong: HR L30, Trend, H2H. Projection model targeted 18.2 pts — actual 28 was 9.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Raynaud's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>Trey Murphy III</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E105" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>WIN — III scored 13 pts vs 21.5 line (-8.5), UNDER hit by 8.5 pts. III played 32 min (-4.4 vs L10 avg of 36.2) — 12% less than expected. Shooting efficiency was hot: 55.6% FG (+11.9% vs L10 avg of 43.7%). 5/9 from the field. Signals that called it correctly: HR L30, Trend, Context, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L10, Defense. Projection model targeted 18.5 pts — actual 13 was 5.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms III's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="4" t="inlineStr">
         <is>
           <t>Dylan Cardwell</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D106" t="n">
+      <c r="D106" s="4" t="n">
         <v>4.5</v>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Cardwell scored 6 pts vs 4.5 line (+1.5), OVER hit by 1.5 pts. Cardwell played 24 min (+6.6 vs L10 avg of 17.0) — 39% more than expected. Shooting efficiency was hot: 100.0% FG (+48.7% vs L10 avg of 51.3%). 3/3 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, Pace (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 5.2 pts — actual 6 was 0.8 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Cardwell in this role.</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:30</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/daily/2026-04-03.xlsx
+++ b/daily/2026-04-03.xlsx
@@ -14632,7 +14632,7 @@
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-04 08:30</t>
+          <t>2026-04-04 13:13</t>
         </is>
       </c>
     </row>
@@ -16184,7 +16184,7 @@
       <c r="I45" s="5" t="n"/>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>2026-04-04 08:30</t>
+          <t>2026-04-04 13:13</t>
         </is>
       </c>
     </row>
@@ -16264,7 +16264,7 @@
       <c r="I47" s="5" t="n"/>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>2026-04-04 08:30</t>
+          <t>2026-04-04 13:13</t>
         </is>
       </c>
     </row>
@@ -16390,7 +16390,7 @@
       <c r="I50" s="5" t="n"/>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>2026-04-04 08:30</t>
+          <t>2026-04-04 13:13</t>
         </is>
       </c>
     </row>
@@ -16562,7 +16562,7 @@
       <c r="I54" s="5" t="n"/>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>2026-04-04 08:30</t>
+          <t>2026-04-04 13:13</t>
         </is>
       </c>
     </row>
